--- a/data/trans_orig/P37A$vacunapreferencia-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37A$vacunapreferencia-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23788</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48061</t>
+          <t>46353</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24412</t>
+          <t>24231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47876</t>
+          <t>48860</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53658</t>
+          <t>53791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85970</t>
+          <t>86970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>983662</t>
+          <t>985370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1007935</t>
+          <t>1007987</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1267237</t>
+          <t>1266253</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1290701</t>
+          <t>1290882</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2260865</t>
+          <t>2259865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2293177</t>
+          <t>2293044</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23693</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48463</t>
+          <t>48407</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23555</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47263</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50583</t>
+          <t>51552</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85508</t>
+          <t>87023</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1644950</t>
+          <t>1645006</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1669720</t>
+          <t>1670380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1540410</t>
+          <t>1539748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1564118</t>
+          <t>1564855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3195578</t>
+          <t>3194063</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3230503</t>
+          <t>3229534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>14978</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34957</t>
+          <t>34471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27092</t>
+          <t>27933</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29098</t>
+          <t>28955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53913</t>
+          <t>55946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516451</t>
+          <t>516937</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537021</t>
+          <t>536430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>449320</t>
+          <t>448479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>466927</t>
+          <t>466184</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>973907</t>
+          <t>971874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>998722</t>
+          <t>998865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74819</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113119</t>
+          <t>111372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67545</t>
+          <t>69680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108075</t>
+          <t>105793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151285</t>
+          <t>152147</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205842</t>
+          <t>207189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3163424</t>
+          <t>3165171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3201724</t>
+          <t>3203179</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3271122</t>
+          <t>3273404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3311652</t>
+          <t>3309517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6449899</t>
+          <t>6448552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6504456</t>
+          <t>6503594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45088</t>
+          <t>44647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24220</t>
+          <t>24027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48223</t>
+          <t>46187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51360</t>
+          <t>50727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83088</t>
+          <t>83483</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>929555</t>
+          <t>929996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>954351</t>
+          <t>953224</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1289574</t>
+          <t>1291610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1313577</t>
+          <t>1313770</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2229352</t>
+          <t>2228957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2261080</t>
+          <t>2261713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45003</t>
+          <t>44284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78082</t>
+          <t>75536</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>40699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69821</t>
+          <t>69341</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107309</t>
+          <t>106222</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1885875</t>
+          <t>1888421</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1918954</t>
+          <t>1919673</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1719100</t>
+          <t>1717104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1740488</t>
+          <t>1739364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3614451</t>
+          <t>3615538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3651939</t>
+          <t>3652419</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16172</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>460453</t>
+          <t>459397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474497</t>
+          <t>474239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442459</t>
+          <t>443281</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455648</t>
+          <t>455654</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>907537</t>
+          <t>907032</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>927434</t>
+          <t>927827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85716</t>
+          <t>85813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126795</t>
+          <t>126463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53873</t>
+          <t>53610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88674</t>
+          <t>86513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147806</t>
+          <t>149151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>201830</t>
+          <t>200712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3292987</t>
+          <t>3293319</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3334066</t>
+          <t>3333969</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3465556</t>
+          <t>3467717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3500357</t>
+          <t>3500620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6772182</t>
+          <t>6773300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6826206</t>
+          <t>6824861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31395</t>
+          <t>32351</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>37228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35482</t>
+          <t>34731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63765</t>
+          <t>63239</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>722952</t>
+          <t>721996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>740462</t>
+          <t>739595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>956811</t>
+          <t>957432</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>978413</t>
+          <t>979207</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1685242</t>
+          <t>1685768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1713525</t>
+          <t>1714276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>36935</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>17376</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40209</t>
+          <t>38861</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37499</t>
+          <t>37322</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66883</t>
+          <t>66439</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2040137</t>
+          <t>2039450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2060852</t>
+          <t>2061455</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1948091</t>
+          <t>1949439</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1971026</t>
+          <t>1970924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3997802</t>
+          <t>3998246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4027186</t>
+          <t>4027363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>16891</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19679</t>
+          <t>20405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>31775</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531734</t>
+          <t>529995</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542895</t>
+          <t>542814</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>529461</t>
+          <t>528735</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>543577</t>
+          <t>542883</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1065698</t>
+          <t>1064252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1083276</t>
+          <t>1083078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41729</t>
+          <t>40334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71409</t>
+          <t>71761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48587</t>
+          <t>50723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81938</t>
+          <t>83115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98494</t>
+          <t>98753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143283</t>
+          <t>142588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3306209</t>
+          <t>3305857</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3335889</t>
+          <t>3337284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3450162</t>
+          <t>3448985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3483513</t>
+          <t>3481377</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6766435</t>
+          <t>6767130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6811224</t>
+          <t>6810965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>41967</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30147</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52761</t>
+          <t>55475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>53583</t>
+          <t>59158</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42598</t>
+          <t>48138</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64008</t>
+          <t>70820</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>92240</t>
+          <t>101125</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78485</t>
+          <t>86699</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109567</t>
+          <t>118352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>476281</t>
+          <t>536562</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>462177</t>
+          <t>523054</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484791</t>
+          <t>546641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>701925</t>
+          <t>762880</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>691500</t>
+          <t>751218</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>712910</t>
+          <t>773900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1178206</t>
+          <t>1299442</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1160879</t>
+          <t>1282215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1191961</t>
+          <t>1313868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>154692</t>
+          <t>173302</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108681</t>
+          <t>147146</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>185789</t>
+          <t>201326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>152132</t>
+          <t>168672</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113786</t>
+          <t>146921</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182899</t>
+          <t>192596</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>306824</t>
+          <t>341974</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>245662</t>
+          <t>309269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>351091</t>
+          <t>379306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2135635</t>
+          <t>2057264</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2104538</t>
+          <t>2029240</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2181646</t>
+          <t>2083420</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2085691</t>
+          <t>2002720</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2054924</t>
+          <t>1978796</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2124037</t>
+          <t>2024471</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4221326</t>
+          <t>4059985</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4177059</t>
+          <t>4022653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4282488</t>
+          <t>4092690</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>56717</t>
+          <t>59167</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42706</t>
+          <t>45018</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72932</t>
+          <t>76389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>58631</t>
+          <t>64919</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47164</t>
+          <t>52877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70953</t>
+          <t>78672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>115348</t>
+          <t>124086</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97594</t>
+          <t>104983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135134</t>
+          <t>145725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>589906</t>
+          <t>652420</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>573691</t>
+          <t>635198</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>603917</t>
+          <t>666569</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>601832</t>
+          <t>669958</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>589510</t>
+          <t>656205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>613299</t>
+          <t>682000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1191738</t>
+          <t>1322378</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1171952</t>
+          <t>1300739</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1209492</t>
+          <t>1341481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>250066</t>
+          <t>274436</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>199253</t>
+          <t>240985</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>285599</t>
+          <t>309044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>264346</t>
+          <t>292749</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>220027</t>
+          <t>264642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>298612</t>
+          <t>321636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>514412</t>
+          <t>567185</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>445984</t>
+          <t>523338</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>569440</t>
+          <t>610179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3201823</t>
+          <t>3246247</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3166290</t>
+          <t>3211639</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3252636</t>
+          <t>3279698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3389448</t>
+          <t>3435558</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3355182</t>
+          <t>3406671</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3433767</t>
+          <t>3463665</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6591271</t>
+          <t>6681805</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6536243</t>
+          <t>6638811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6659699</t>
+          <t>6725652</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
